--- a/data/processed/artilheiros.xlsx
+++ b/data/processed/artilheiros.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,45 +424,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nome_jogador</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>posicao</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>nacionalidade</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>id_time</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>nome_time</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>partidas_jogadas</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gols</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>assistencias</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>penaltis</t>
         </is>
@@ -472,275 +452,147 @@
       <c r="A2" t="n">
         <v>192070</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Kevin Viveros</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+      <c r="B2" t="n">
+        <v>1768</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>1768</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CA Paranaense</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="F2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1077</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pedro</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1783</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CR Flamengo</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H3" t="n">
+        <v>37833</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1767</v>
+      </c>
+      <c r="C3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>37833</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Carlos Vinícius</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+        <v>1077</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1783</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>1767</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grêmio FBPA</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>157533</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>John Kennedy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+      <c r="B5" t="n">
+        <v>1765</v>
+      </c>
+      <c r="C5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>1765</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Fluminense FC</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>169022</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Breno Lopes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4241</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>4241</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Coritiba FBC</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>149704</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Danilo dos Santos de Oliveira</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+      <c r="B7" t="n">
+        <v>1770</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>1770</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Botafogo FR</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>1723</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Arthur Cabral</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+      <c r="B8" t="n">
+        <v>1770</v>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>1770</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Botafogo FR</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>17</v>
-      </c>
-      <c r="H8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>140873</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Luciano Juba</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+      <c r="B9" t="n">
+        <v>1777</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>1777</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>EC Bahia</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>15</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="F9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -748,35 +600,19 @@
       <c r="A10" t="n">
         <v>1327</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Gabriel Barbosa</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+      <c r="B10" t="n">
+        <v>6685</v>
+      </c>
+      <c r="C10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>6685</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Santos FC</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>13</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="n">
+      <c r="F10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -784,35 +620,19 @@
       <c r="A11" t="n">
         <v>170698</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>José Manuel López</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1769</v>
+      </c>
+      <c r="C11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>1769</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SE Palmeiras</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>17</v>
-      </c>
-      <c r="H11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/processed/artilheiros.xlsx
+++ b/data/processed/artilheiros.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,20 +429,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>partidas_jogadas</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>gols</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>assistencias</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>penaltis</t>
         </is>
@@ -456,15 +451,12 @@
         <v>1768</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -476,13 +468,10 @@
         <v>1767</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -494,15 +483,12 @@
         <v>1783</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,15 +498,12 @@
         <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -530,15 +513,12 @@
         <v>4241</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -548,15 +528,12 @@
         <v>1770</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -566,15 +543,12 @@
         <v>1770</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -584,15 +558,12 @@
         <v>1777</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -604,15 +575,12 @@
         <v>6685</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -624,15 +592,12 @@
         <v>1769</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/processed/artilheiros.xlsx
+++ b/data/processed/artilheiros.xlsx
@@ -451,10 +451,10 @@
         <v>1768</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -462,33 +462,33 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>37833</v>
+        <v>1077</v>
       </c>
       <c r="B3" t="n">
-        <v>1767</v>
+        <v>1783</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1077</v>
+        <v>37833</v>
       </c>
       <c r="B4" t="n">
-        <v>1783</v>
+        <v>1767</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -537,10 +537,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1723</v>
+        <v>3137</v>
       </c>
       <c r="B8" t="n">
-        <v>1770</v>
+        <v>1776</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -548,14 +548,16 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>140873</v>
+        <v>1723</v>
       </c>
       <c r="B9" t="n">
-        <v>1777</v>
+        <v>1770</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -563,41 +565,41 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1327</v>
+        <v>140873</v>
       </c>
       <c r="B10" t="n">
-        <v>6685</v>
+        <v>1777</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>170698</v>
+        <v>1327</v>
       </c>
       <c r="B11" t="n">
-        <v>1769</v>
+        <v>6685</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
